--- a/common/template/document/tabel_teachers_budget.xlsx
+++ b/common/template/document/tabel_teachers_budget.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="119">
   <si>
     <t>явок</t>
   </si>
@@ -32,9 +32,6 @@
   </si>
   <si>
     <t xml:space="preserve">  по  ОКПО</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                        (должность)                  (подпись)                (расшифровка подписи)</t>
   </si>
   <si>
     <t xml:space="preserve">          Дата</t>
@@ -107,9 +104,6 @@
     <t>(первичный - 0; корректирующий - 1, 2 и так далее)</t>
   </si>
   <si>
-    <t>Директор</t>
-  </si>
-  <si>
     <t>Табель № [doc.tabel_num]</t>
   </si>
   <si>
@@ -117,9 +111,6 @@
   </si>
   <si>
     <t>[doc.org_briefname]</t>
-  </si>
-  <si>
-    <t>[doc.departments]</t>
   </si>
   <si>
     <t>(подпись)</t>
@@ -263,16 +254,10 @@
     <t xml:space="preserve">Исполнитель </t>
   </si>
   <si>
-    <t>_________</t>
-  </si>
-  <si>
     <t>[doc.doc_accountant_post]</t>
   </si>
   <si>
     <t>[doc.doc_accountant_iof]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">     учета использования рабочего времени ([doc.subject_type_name])</t>
   </si>
   <si>
     <t>ИТОГО:</t>
@@ -376,6 +361,27 @@
   <si>
     <t>[a.days.time_total;ope=tbs:num]</t>
   </si>
+  <si>
+    <t xml:space="preserve">     учета использования рабочего времени</t>
+  </si>
+  <si>
+    <t>Педагогические работники</t>
+  </si>
+  <si>
+    <t>Ответственный исполнитель - Директор</t>
+  </si>
+  <si>
+    <t>первичный</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                             (должность)                  (подпись)                (расшифровка подписи)</t>
+  </si>
+  <si>
+    <t>(расшифровка подписи)</t>
+  </si>
 </sst>
 </file>
 
@@ -384,7 +390,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial Cyr"/>
@@ -439,12 +445,6 @@
     </font>
     <font>
       <b/>
-      <sz val="8"/>
-      <name val="Arial Cyr"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <u/>
       <sz val="8"/>
       <name val="Arial Cyr"/>
       <charset val="204"/>
@@ -851,7 +851,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -866,9 +866,6 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -890,13 +887,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -923,7 +914,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -948,7 +938,39 @@
     <xf numFmtId="164" fontId="9" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -980,36 +1002,17 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1396,310 +1399,312 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:46" x14ac:dyDescent="0.2">
-      <c r="AG1" s="55"/>
-      <c r="AH1" s="55"/>
-      <c r="AI1" s="55"/>
-      <c r="AJ1" s="55"/>
-      <c r="AK1" s="55"/>
+      <c r="AG1" s="59"/>
+      <c r="AH1" s="59"/>
+      <c r="AI1" s="59"/>
+      <c r="AJ1" s="59"/>
+      <c r="AK1" s="59"/>
     </row>
     <row r="2" spans="1:46" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H2" s="59" t="s">
-        <v>28</v>
-      </c>
-      <c r="I2" s="59"/>
-      <c r="J2" s="59"/>
-      <c r="K2" s="59"/>
-      <c r="L2" s="59"/>
-      <c r="M2" s="59"/>
-      <c r="N2" s="59"/>
-      <c r="O2" s="59"/>
-      <c r="P2" s="59"/>
-      <c r="Q2" s="59"/>
-      <c r="R2" s="59"/>
-      <c r="S2" s="59"/>
-      <c r="T2" s="59"/>
-      <c r="U2" s="59"/>
+      <c r="H2" s="63" t="s">
+        <v>26</v>
+      </c>
+      <c r="I2" s="63"/>
+      <c r="J2" s="63"/>
+      <c r="K2" s="63"/>
+      <c r="L2" s="63"/>
+      <c r="M2" s="63"/>
+      <c r="N2" s="63"/>
+      <c r="O2" s="63"/>
+      <c r="P2" s="63"/>
+      <c r="Q2" s="63"/>
+      <c r="R2" s="63"/>
+      <c r="S2" s="63"/>
+      <c r="T2" s="63"/>
+      <c r="U2" s="63"/>
     </row>
     <row r="3" spans="1:46" s="1" customFormat="1" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E3" s="64" t="s">
-        <v>82</v>
-      </c>
-      <c r="F3" s="64"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
-      <c r="J3" s="64"/>
-      <c r="K3" s="64"/>
-      <c r="L3" s="64"/>
-      <c r="M3" s="64"/>
-      <c r="N3" s="64"/>
-      <c r="O3" s="64"/>
-      <c r="P3" s="64"/>
-      <c r="Q3" s="64"/>
-      <c r="R3" s="64"/>
-      <c r="S3" s="64"/>
-      <c r="T3" s="64"/>
-      <c r="U3" s="64"/>
-      <c r="V3" s="64"/>
-      <c r="W3" s="64"/>
-      <c r="X3" s="64"/>
-      <c r="Y3" s="64"/>
-      <c r="AI3" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="AJ3" s="28"/>
-      <c r="AK3" s="29"/>
+      <c r="E3" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="F3" s="68"/>
+      <c r="G3" s="68"/>
+      <c r="H3" s="68"/>
+      <c r="I3" s="68"/>
+      <c r="J3" s="68"/>
+      <c r="K3" s="68"/>
+      <c r="L3" s="68"/>
+      <c r="M3" s="68"/>
+      <c r="N3" s="68"/>
+      <c r="O3" s="68"/>
+      <c r="P3" s="68"/>
+      <c r="Q3" s="68"/>
+      <c r="R3" s="68"/>
+      <c r="S3" s="68"/>
+      <c r="T3" s="68"/>
+      <c r="U3" s="68"/>
+      <c r="V3" s="68"/>
+      <c r="W3" s="68"/>
+      <c r="X3" s="68"/>
+      <c r="Y3" s="68"/>
+      <c r="AI3" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="AJ3" s="23"/>
+      <c r="AK3" s="24"/>
     </row>
     <row r="4" spans="1:46" s="1" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="AE4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="AI4" s="56" t="s">
-        <v>16</v>
-      </c>
-      <c r="AJ4" s="57"/>
-      <c r="AK4" s="58"/>
+        <v>18</v>
+      </c>
+      <c r="AI4" s="60" t="s">
+        <v>15</v>
+      </c>
+      <c r="AJ4" s="61"/>
+      <c r="AK4" s="62"/>
     </row>
     <row r="5" spans="1:46" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G5" s="69" t="s">
-        <v>29</v>
-      </c>
-      <c r="H5" s="70"/>
-      <c r="I5" s="70"/>
-      <c r="J5" s="70"/>
-      <c r="K5" s="70"/>
-      <c r="L5" s="70"/>
-      <c r="M5" s="70"/>
-      <c r="N5" s="70"/>
-      <c r="O5" s="70"/>
-      <c r="P5" s="70"/>
-      <c r="Q5" s="70"/>
-      <c r="R5" s="70"/>
-      <c r="S5" s="70"/>
-      <c r="T5" s="70"/>
-      <c r="U5" s="70"/>
-      <c r="V5" s="70"/>
-      <c r="W5" s="70"/>
-      <c r="X5" s="70"/>
-      <c r="Y5" s="70"/>
+      <c r="G5" s="54" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="54"/>
+      <c r="K5" s="54"/>
+      <c r="L5" s="54"/>
+      <c r="M5" s="54"/>
+      <c r="N5" s="54"/>
+      <c r="O5" s="54"/>
+      <c r="P5" s="54"/>
+      <c r="Q5" s="54"/>
+      <c r="R5" s="54"/>
+      <c r="S5" s="54"/>
+      <c r="T5" s="54"/>
+      <c r="U5" s="54"/>
+      <c r="V5" s="54"/>
+      <c r="W5" s="54"/>
+      <c r="X5" s="54"/>
+      <c r="Y5" s="54"/>
       <c r="AF5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AI5" s="61" t="s">
-        <v>43</v>
-      </c>
-      <c r="AJ5" s="62"/>
-      <c r="AK5" s="63"/>
+        <v>6</v>
+      </c>
+      <c r="AI5" s="65"/>
+      <c r="AJ5" s="66"/>
+      <c r="AK5" s="67"/>
     </row>
     <row r="6" spans="1:46" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="71" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" s="71"/>
-      <c r="D6" s="60" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" s="60"/>
-      <c r="F6" s="60"/>
-      <c r="G6" s="60"/>
-      <c r="H6" s="60"/>
-      <c r="I6" s="60"/>
-      <c r="J6" s="60"/>
-      <c r="K6" s="60"/>
-      <c r="L6" s="60"/>
-      <c r="M6" s="60"/>
-      <c r="N6" s="60"/>
-      <c r="O6" s="60"/>
-      <c r="P6" s="60"/>
-      <c r="Q6" s="60"/>
-      <c r="R6" s="60"/>
-      <c r="S6" s="60"/>
-      <c r="T6" s="60"/>
-      <c r="U6" s="60"/>
-      <c r="V6" s="60"/>
-      <c r="W6" s="60"/>
-      <c r="X6" s="60"/>
-      <c r="Y6" s="60"/>
-      <c r="Z6" s="60"/>
-      <c r="AA6" s="60"/>
-      <c r="AB6" s="60"/>
+      <c r="A6" s="55" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="55"/>
+      <c r="D6" s="64" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="64"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="64"/>
+      <c r="K6" s="64"/>
+      <c r="L6" s="64"/>
+      <c r="M6" s="64"/>
+      <c r="N6" s="64"/>
+      <c r="O6" s="64"/>
+      <c r="P6" s="64"/>
+      <c r="Q6" s="64"/>
+      <c r="R6" s="64"/>
+      <c r="S6" s="64"/>
+      <c r="T6" s="64"/>
+      <c r="U6" s="64"/>
+      <c r="V6" s="64"/>
+      <c r="W6" s="64"/>
+      <c r="X6" s="64"/>
+      <c r="Y6" s="64"/>
+      <c r="Z6" s="64"/>
+      <c r="AA6" s="64"/>
+      <c r="AB6" s="64"/>
       <c r="AF6" s="1" t="s">
         <v>5</v>
       </c>
       <c r="AI6" s="7"/>
       <c r="AJ6" s="8" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="AK6" s="9"/>
     </row>
     <row r="7" spans="1:46" s="1" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="53" t="s">
+        <v>113</v>
+      </c>
+      <c r="E7" s="53"/>
+      <c r="F7" s="53"/>
+      <c r="G7" s="53"/>
+      <c r="H7" s="53"/>
+      <c r="I7" s="53"/>
+      <c r="J7" s="53"/>
+      <c r="K7" s="53"/>
+      <c r="L7" s="53"/>
+      <c r="M7" s="53"/>
+      <c r="N7" s="53"/>
+      <c r="O7" s="53"/>
+      <c r="P7" s="53"/>
+      <c r="Q7" s="53"/>
+      <c r="R7" s="53"/>
+      <c r="S7" s="53"/>
+      <c r="T7" s="53"/>
+      <c r="U7" s="53"/>
+      <c r="V7" s="53"/>
+      <c r="W7" s="53"/>
+      <c r="X7" s="53"/>
+      <c r="Y7" s="53"/>
+      <c r="Z7" s="53"/>
+      <c r="AA7" s="53"/>
+      <c r="AB7" s="53"/>
+      <c r="AI7" s="11"/>
+      <c r="AJ7" s="12"/>
+      <c r="AK7" s="13"/>
+    </row>
+    <row r="8" spans="1:46" s="1" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="55" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="55"/>
+      <c r="D8" s="58" t="s">
+        <v>115</v>
+      </c>
+      <c r="E8" s="58"/>
+      <c r="F8" s="58"/>
+      <c r="G8" s="58"/>
+      <c r="H8" s="58"/>
+      <c r="I8" s="58"/>
+      <c r="J8" s="58"/>
+      <c r="K8" s="58"/>
+      <c r="L8" s="58"/>
+      <c r="M8" s="58"/>
+      <c r="N8" s="58"/>
+      <c r="O8" s="58"/>
+      <c r="P8" s="58"/>
+      <c r="Q8" s="58"/>
+      <c r="R8" s="58"/>
+      <c r="S8" s="58"/>
+      <c r="T8" s="58"/>
+      <c r="U8" s="58"/>
+      <c r="V8" s="58"/>
+      <c r="W8" s="58"/>
+      <c r="X8" s="58"/>
+      <c r="Y8" s="58"/>
+      <c r="Z8" s="58"/>
+      <c r="AA8" s="58"/>
+      <c r="AB8" s="58"/>
+      <c r="AC8" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D7" s="68" t="s">
-        <v>31</v>
-      </c>
-      <c r="E7" s="68"/>
-      <c r="F7" s="68"/>
-      <c r="G7" s="68"/>
-      <c r="H7" s="68"/>
-      <c r="I7" s="68"/>
-      <c r="J7" s="68"/>
-      <c r="K7" s="68"/>
-      <c r="L7" s="68"/>
-      <c r="M7" s="68"/>
-      <c r="N7" s="68"/>
-      <c r="O7" s="68"/>
-      <c r="P7" s="68"/>
-      <c r="Q7" s="68"/>
-      <c r="R7" s="68"/>
-      <c r="S7" s="68"/>
-      <c r="T7" s="68"/>
-      <c r="U7" s="68"/>
-      <c r="V7" s="68"/>
-      <c r="W7" s="68"/>
-      <c r="X7" s="68"/>
-      <c r="Y7" s="68"/>
-      <c r="Z7" s="68"/>
-      <c r="AA7" s="68"/>
-      <c r="AB7" s="68"/>
-      <c r="AI7" s="14"/>
-      <c r="AJ7" s="15"/>
-      <c r="AK7" s="16"/>
-    </row>
-    <row r="8" spans="1:46" s="1" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="71" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="71"/>
-      <c r="D8" s="74">
-        <v>0</v>
-      </c>
-      <c r="E8" s="74"/>
-      <c r="F8" s="74"/>
-      <c r="G8" s="74"/>
-      <c r="H8" s="74"/>
-      <c r="I8" s="74"/>
-      <c r="J8" s="74"/>
-      <c r="K8" s="74"/>
-      <c r="L8" s="74"/>
-      <c r="M8" s="74"/>
-      <c r="N8" s="74"/>
-      <c r="O8" s="74"/>
-      <c r="P8" s="74"/>
-      <c r="Q8" s="74"/>
-      <c r="R8" s="74"/>
-      <c r="S8" s="74"/>
-      <c r="T8" s="74"/>
-      <c r="U8" s="74"/>
-      <c r="V8" s="74"/>
-      <c r="W8" s="74"/>
-      <c r="X8" s="74"/>
-      <c r="Y8" s="74"/>
-      <c r="Z8" s="74"/>
-      <c r="AA8" s="74"/>
-      <c r="AB8" s="74"/>
-      <c r="AC8" s="1" t="s">
+      <c r="AI8" s="11"/>
+      <c r="AJ8" s="12"/>
+      <c r="AK8" s="13" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="9" spans="1:46" s="1" customFormat="1" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="G9" s="10"/>
+      <c r="K9" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z9" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AI8" s="14"/>
-      <c r="AJ8" s="15"/>
-      <c r="AK8" s="16"/>
-    </row>
-    <row r="9" spans="1:46" s="1" customFormat="1" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="G9" s="13"/>
-      <c r="K9" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="Z9" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="AE9" s="17"/>
-      <c r="AI9" s="10"/>
-      <c r="AJ9" s="11"/>
-      <c r="AK9" s="12"/>
+      <c r="AE9" s="14"/>
+      <c r="AI9" s="69" t="s">
+        <v>40</v>
+      </c>
+      <c r="AJ9" s="70"/>
+      <c r="AK9" s="71"/>
     </row>
     <row r="10" spans="1:46" s="1" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="23"/>
-      <c r="B10" s="23"/>
-      <c r="C10" s="23"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="23"/>
-      <c r="F10" s="23"/>
-      <c r="G10" s="23"/>
-      <c r="H10" s="23"/>
-      <c r="I10" s="23"/>
-      <c r="J10" s="23"/>
-      <c r="K10" s="23"/>
-      <c r="L10" s="23"/>
-      <c r="M10" s="23"/>
-      <c r="N10" s="23"/>
-      <c r="O10" s="23"/>
-      <c r="P10" s="23"/>
-      <c r="Q10" s="23"/>
-      <c r="R10" s="23"/>
-      <c r="S10" s="23"/>
-      <c r="T10" s="23"/>
-      <c r="U10" s="23"/>
-      <c r="V10" s="23"/>
-      <c r="W10" s="23"/>
-      <c r="X10" s="23"/>
-      <c r="Y10" s="23"/>
-      <c r="Z10" s="23"/>
-      <c r="AA10" s="23"/>
-      <c r="AB10" s="23"/>
-      <c r="AC10" s="23"/>
-      <c r="AD10" s="23"/>
-      <c r="AE10" s="23"/>
-      <c r="AF10" s="23"/>
-      <c r="AG10" s="23"/>
-      <c r="AH10" s="23"/>
-      <c r="AI10" s="23"/>
-      <c r="AJ10" s="23"/>
-      <c r="AK10" s="23"/>
+      <c r="A10" s="19"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="19"/>
+      <c r="M10" s="19"/>
+      <c r="N10" s="19"/>
+      <c r="O10" s="19"/>
+      <c r="P10" s="19"/>
+      <c r="Q10" s="19"/>
+      <c r="R10" s="19"/>
+      <c r="S10" s="19"/>
+      <c r="T10" s="19"/>
+      <c r="U10" s="19"/>
+      <c r="V10" s="19"/>
+      <c r="W10" s="19"/>
+      <c r="X10" s="19"/>
+      <c r="Y10" s="19"/>
+      <c r="Z10" s="19"/>
+      <c r="AA10" s="19"/>
+      <c r="AB10" s="19"/>
+      <c r="AC10" s="19"/>
+      <c r="AD10" s="19"/>
+      <c r="AE10" s="19"/>
+      <c r="AF10" s="19"/>
+      <c r="AG10" s="19"/>
+      <c r="AH10" s="19"/>
+      <c r="AI10" s="19"/>
+      <c r="AJ10" s="19"/>
+      <c r="AK10" s="19"/>
     </row>
     <row r="11" spans="1:46" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="19"/>
-      <c r="B11" s="72" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="73"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="30"/>
-      <c r="F11" s="22"/>
-      <c r="G11" s="22"/>
-      <c r="H11" s="22"/>
-      <c r="I11" s="22"/>
-      <c r="J11" s="22"/>
-      <c r="K11" s="22"/>
-      <c r="L11" s="22"/>
-      <c r="M11" s="22"/>
-      <c r="N11" s="22"/>
-      <c r="O11" s="22"/>
-      <c r="P11" s="22"/>
-      <c r="Q11" s="22"/>
-      <c r="R11" s="22"/>
-      <c r="S11" s="22"/>
-      <c r="T11" s="40" t="s">
+      <c r="A11" s="16"/>
+      <c r="B11" s="56" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="57"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="49"/>
+      <c r="G11" s="49"/>
+      <c r="H11" s="49"/>
+      <c r="I11" s="49"/>
+      <c r="J11" s="49"/>
+      <c r="K11" s="49"/>
+      <c r="L11" s="49"/>
+      <c r="M11" s="49"/>
+      <c r="N11" s="49"/>
+      <c r="O11" s="49"/>
+      <c r="P11" s="49"/>
+      <c r="Q11" s="49"/>
+      <c r="R11" s="49"/>
+      <c r="S11" s="49"/>
+      <c r="T11" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="U11" s="22"/>
-      <c r="V11" s="22"/>
-      <c r="W11" s="22"/>
-      <c r="X11" s="22"/>
-      <c r="Y11" s="22"/>
-      <c r="Z11" s="22"/>
-      <c r="AA11" s="22"/>
-      <c r="AB11" s="22"/>
-      <c r="AC11" s="22"/>
-      <c r="AD11" s="22"/>
-      <c r="AE11" s="22"/>
-      <c r="AF11" s="22"/>
-      <c r="AG11" s="22"/>
-      <c r="AH11" s="22"/>
-      <c r="AI11" s="22"/>
-      <c r="AJ11" s="22"/>
-      <c r="AK11" s="24"/>
+      <c r="U11" s="49"/>
+      <c r="V11" s="49"/>
+      <c r="W11" s="49"/>
+      <c r="X11" s="49"/>
+      <c r="Y11" s="49"/>
+      <c r="Z11" s="49"/>
+      <c r="AA11" s="49"/>
+      <c r="AB11" s="49"/>
+      <c r="AC11" s="49"/>
+      <c r="AD11" s="49"/>
+      <c r="AE11" s="49"/>
+      <c r="AF11" s="49"/>
+      <c r="AG11" s="49"/>
+      <c r="AH11" s="49"/>
+      <c r="AI11" s="49"/>
+      <c r="AJ11" s="49"/>
+      <c r="AK11" s="48"/>
       <c r="AL11" s="1"/>
       <c r="AM11" s="1"/>
       <c r="AN11" s="1"/>
@@ -1711,14 +1716,14 @@
       <c r="AT11" s="1"/>
     </row>
     <row r="12" spans="1:46" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="20" t="s">
+      <c r="A12" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="B12" s="65" t="s">
-        <v>44</v>
-      </c>
-      <c r="C12" s="65" t="s">
-        <v>45</v>
+      <c r="B12" s="50" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" s="50" t="s">
+        <v>42</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="2"/>
@@ -1737,7 +1742,7 @@
       <c r="R12" s="4"/>
       <c r="S12" s="4"/>
       <c r="T12" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U12" s="3"/>
       <c r="V12" s="4"/>
@@ -1756,7 +1761,7 @@
       <c r="AI12" s="4"/>
       <c r="AJ12" s="4"/>
       <c r="AK12" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AL12" s="1"/>
       <c r="AM12" s="1"/>
@@ -1769,11 +1774,11 @@
       <c r="AT12" s="1"/>
     </row>
     <row r="13" spans="1:46" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="20" t="s">
+      <c r="A13" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="B13" s="66"/>
-      <c r="C13" s="66"/>
+      <c r="B13" s="51"/>
+      <c r="C13" s="51"/>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
@@ -1791,7 +1796,7 @@
       <c r="R13" s="3"/>
       <c r="S13" s="3"/>
       <c r="T13" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U13" s="3"/>
       <c r="V13" s="3"/>
@@ -1809,8 +1814,8 @@
       <c r="AH13" s="3"/>
       <c r="AI13" s="3"/>
       <c r="AJ13" s="3"/>
-      <c r="AK13" s="20" t="s">
-        <v>10</v>
+      <c r="AK13" s="17" t="s">
+        <v>9</v>
       </c>
       <c r="AL13" s="1"/>
       <c r="AM13" s="1"/>
@@ -1823,9 +1828,9 @@
       <c r="AT13" s="1"/>
     </row>
     <row r="14" spans="1:46" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="20"/>
-      <c r="B14" s="66"/>
-      <c r="C14" s="66"/>
+      <c r="A14" s="17"/>
+      <c r="B14" s="51"/>
+      <c r="C14" s="51"/>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1875,7 +1880,7 @@
         <v>15</v>
       </c>
       <c r="T14" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="U14" s="3">
         <v>16</v>
@@ -1925,8 +1930,8 @@
       <c r="AJ14" s="3">
         <v>31</v>
       </c>
-      <c r="AK14" s="20" t="s">
-        <v>13</v>
+      <c r="AK14" s="17" t="s">
+        <v>12</v>
       </c>
       <c r="AL14" s="1"/>
       <c r="AM14" s="1"/>
@@ -1939,11 +1944,11 @@
       <c r="AT14" s="1"/>
     </row>
     <row r="15" spans="1:46" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="20"/>
-      <c r="B15" s="66"/>
-      <c r="C15" s="66"/>
+      <c r="A15" s="17"/>
+      <c r="B15" s="51"/>
+      <c r="C15" s="51"/>
       <c r="D15" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
@@ -1979,7 +1984,7 @@
       <c r="AH15" s="3"/>
       <c r="AI15" s="3"/>
       <c r="AJ15" s="3"/>
-      <c r="AK15" s="20" t="s">
+      <c r="AK15" s="17" t="s">
         <v>0</v>
       </c>
       <c r="AL15" s="1"/>
@@ -1993,9 +1998,9 @@
       <c r="AT15" s="1"/>
     </row>
     <row r="16" spans="1:46" ht="9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="20"/>
-      <c r="B16" s="66"/>
-      <c r="C16" s="66"/>
+      <c r="A16" s="17"/>
+      <c r="B16" s="51"/>
+      <c r="C16" s="51"/>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -2013,7 +2018,7 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
@@ -2031,8 +2036,8 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
-      <c r="AK16" s="20" t="s">
-        <v>14</v>
+      <c r="AK16" s="17" t="s">
+        <v>13</v>
       </c>
       <c r="AL16" s="1"/>
       <c r="AM16" s="1"/>
@@ -2045,9 +2050,9 @@
       <c r="AT16" s="1"/>
     </row>
     <row r="17" spans="1:46" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="20"/>
-      <c r="B17" s="67"/>
-      <c r="C17" s="67"/>
+      <c r="A17" s="17"/>
+      <c r="B17" s="52"/>
+      <c r="C17" s="52"/>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
@@ -2064,8 +2069,8 @@
       <c r="Q17" s="3"/>
       <c r="R17" s="3"/>
       <c r="S17" s="3"/>
-      <c r="T17" s="21" t="s">
-        <v>15</v>
+      <c r="T17" s="18" t="s">
+        <v>14</v>
       </c>
       <c r="U17" s="3"/>
       <c r="V17" s="3"/>
@@ -2084,7 +2089,7 @@
       <c r="AI17" s="3"/>
       <c r="AJ17" s="3"/>
       <c r="AK17" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AL17" s="1"/>
       <c r="AM17" s="1"/>
@@ -2103,109 +2108,109 @@
       <c r="B18" s="6">
         <v>2</v>
       </c>
-      <c r="C18" s="24">
+      <c r="C18" s="48">
         <v>3</v>
       </c>
-      <c r="D18" s="24">
+      <c r="D18" s="48">
         <v>4</v>
       </c>
-      <c r="E18" s="24">
+      <c r="E18" s="48">
         <v>5</v>
       </c>
-      <c r="F18" s="24">
+      <c r="F18" s="48">
         <v>6</v>
       </c>
-      <c r="G18" s="24">
+      <c r="G18" s="48">
         <v>7</v>
       </c>
-      <c r="H18" s="24">
+      <c r="H18" s="48">
         <v>8</v>
       </c>
-      <c r="I18" s="24">
+      <c r="I18" s="48">
         <v>9</v>
       </c>
-      <c r="J18" s="24">
+      <c r="J18" s="48">
         <v>10</v>
       </c>
-      <c r="K18" s="24">
+      <c r="K18" s="48">
         <v>11</v>
       </c>
-      <c r="L18" s="24">
+      <c r="L18" s="48">
         <v>12</v>
       </c>
-      <c r="M18" s="24">
+      <c r="M18" s="48">
         <v>13</v>
       </c>
-      <c r="N18" s="24">
+      <c r="N18" s="48">
         <v>14</v>
       </c>
-      <c r="O18" s="24">
+      <c r="O18" s="48">
         <v>15</v>
       </c>
-      <c r="P18" s="24">
+      <c r="P18" s="48">
         <v>16</v>
       </c>
-      <c r="Q18" s="24">
+      <c r="Q18" s="48">
         <v>17</v>
       </c>
-      <c r="R18" s="24">
+      <c r="R18" s="48">
         <v>18</v>
       </c>
-      <c r="S18" s="24">
+      <c r="S18" s="48">
         <v>19</v>
       </c>
-      <c r="T18" s="24">
+      <c r="T18" s="48">
         <v>20</v>
       </c>
-      <c r="U18" s="24">
+      <c r="U18" s="48">
         <v>21</v>
       </c>
-      <c r="V18" s="24">
+      <c r="V18" s="48">
         <v>22</v>
       </c>
-      <c r="W18" s="24">
+      <c r="W18" s="48">
         <v>23</v>
       </c>
-      <c r="X18" s="24">
+      <c r="X18" s="48">
         <v>24</v>
       </c>
-      <c r="Y18" s="24">
+      <c r="Y18" s="48">
         <v>25</v>
       </c>
-      <c r="Z18" s="24">
+      <c r="Z18" s="48">
         <v>26</v>
       </c>
-      <c r="AA18" s="24">
+      <c r="AA18" s="48">
         <v>27</v>
       </c>
-      <c r="AB18" s="24">
+      <c r="AB18" s="48">
         <v>28</v>
       </c>
-      <c r="AC18" s="24">
+      <c r="AC18" s="48">
         <v>29</v>
       </c>
-      <c r="AD18" s="24">
+      <c r="AD18" s="48">
         <v>30</v>
       </c>
-      <c r="AE18" s="24">
+      <c r="AE18" s="48">
         <v>31</v>
       </c>
-      <c r="AF18" s="24">
+      <c r="AF18" s="48">
         <v>32</v>
       </c>
-      <c r="AG18" s="24">
+      <c r="AG18" s="48">
         <v>33</v>
       </c>
-      <c r="AH18" s="24">
+      <c r="AH18" s="48">
         <v>34</v>
       </c>
-      <c r="AI18" s="24">
+      <c r="AI18" s="48">
         <v>35</v>
       </c>
-      <c r="AJ18" s="24">
+      <c r="AJ18" s="48">
         <v>36</v>
       </c>
-      <c r="AK18" s="24">
+      <c r="AK18" s="48">
         <v>37</v>
       </c>
       <c r="AL18" s="1"/>
@@ -2218,413 +2223,443 @@
       <c r="AS18" s="1"/>
       <c r="AT18" s="1"/>
     </row>
-    <row r="19" spans="1:46" s="47" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="42" t="s">
-        <v>41</v>
-      </c>
-      <c r="B19" s="43" t="s">
+    <row r="19" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="36" t="s">
         <v>38</v>
       </c>
-      <c r="C19" s="43" t="s">
+      <c r="B19" s="37" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="D19" s="37" t="s">
+        <v>37</v>
+      </c>
+      <c r="E19" s="37" t="s">
+        <v>79</v>
+      </c>
+      <c r="F19" s="37" t="s">
+        <v>80</v>
+      </c>
+      <c r="G19" s="37" t="s">
+        <v>81</v>
+      </c>
+      <c r="H19" s="37" t="s">
+        <v>82</v>
+      </c>
+      <c r="I19" s="37" t="s">
+        <v>83</v>
+      </c>
+      <c r="J19" s="37" t="s">
+        <v>84</v>
+      </c>
+      <c r="K19" s="37" t="s">
+        <v>85</v>
+      </c>
+      <c r="L19" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="M19" s="37" t="s">
+        <v>87</v>
+      </c>
+      <c r="N19" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="O19" s="37" t="s">
+        <v>89</v>
+      </c>
+      <c r="P19" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q19" s="37" t="s">
+        <v>91</v>
+      </c>
+      <c r="R19" s="37" t="s">
+        <v>92</v>
+      </c>
+      <c r="S19" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="T19" s="44" t="s">
+        <v>110</v>
+      </c>
+      <c r="U19" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="V19" s="37" t="s">
+        <v>95</v>
+      </c>
+      <c r="W19" s="37" t="s">
+        <v>96</v>
+      </c>
+      <c r="X19" s="37" t="s">
+        <v>97</v>
+      </c>
+      <c r="Y19" s="37" t="s">
+        <v>98</v>
+      </c>
+      <c r="Z19" s="37" t="s">
+        <v>99</v>
+      </c>
+      <c r="AA19" s="37" t="s">
+        <v>100</v>
+      </c>
+      <c r="AB19" s="37" t="s">
+        <v>101</v>
+      </c>
+      <c r="AC19" s="37" t="s">
+        <v>102</v>
+      </c>
+      <c r="AD19" s="37" t="s">
+        <v>103</v>
+      </c>
+      <c r="AE19" s="37" t="s">
+        <v>104</v>
+      </c>
+      <c r="AF19" s="37" t="s">
+        <v>105</v>
+      </c>
+      <c r="AG19" s="37" t="s">
+        <v>106</v>
+      </c>
+      <c r="AH19" s="37" t="s">
+        <v>107</v>
+      </c>
+      <c r="AI19" s="37" t="s">
+        <v>108</v>
+      </c>
+      <c r="AJ19" s="37" t="s">
+        <v>109</v>
+      </c>
+      <c r="AK19" s="44" t="s">
+        <v>111</v>
+      </c>
+      <c r="AL19" s="1"/>
+      <c r="AM19" s="1"/>
+      <c r="AN19" s="1"/>
+      <c r="AO19" s="1"/>
+      <c r="AP19" s="1"/>
+      <c r="AQ19" s="1"/>
+      <c r="AR19" s="1"/>
+      <c r="AS19" s="1"/>
+      <c r="AT19" s="1"/>
+    </row>
+    <row r="20" spans="1:46" s="41" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="D19" s="43" t="s">
-        <v>40</v>
-      </c>
-      <c r="E19" s="44" t="s">
+      <c r="B20" s="43"/>
+      <c r="C20" s="43"/>
+      <c r="D20" s="43"/>
+      <c r="E20" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="F20" s="38" t="s">
+        <v>44</v>
+      </c>
+      <c r="G20" s="38" t="s">
+        <v>45</v>
+      </c>
+      <c r="H20" s="38" t="s">
         <v>46</v>
       </c>
-      <c r="F19" s="44" t="s">
+      <c r="I20" s="38" t="s">
         <v>47</v>
       </c>
-      <c r="G19" s="44" t="s">
+      <c r="J20" s="38" t="s">
         <v>48</v>
       </c>
-      <c r="H19" s="44" t="s">
+      <c r="K20" s="38" t="s">
         <v>49</v>
       </c>
-      <c r="I19" s="44" t="s">
+      <c r="L20" s="38" t="s">
         <v>50</v>
       </c>
-      <c r="J19" s="44" t="s">
+      <c r="M20" s="38" t="s">
         <v>51</v>
       </c>
-      <c r="K19" s="44" t="s">
+      <c r="N20" s="38" t="s">
         <v>52</v>
       </c>
-      <c r="L19" s="44" t="s">
+      <c r="O20" s="38" t="s">
         <v>53</v>
       </c>
-      <c r="M19" s="44" t="s">
+      <c r="P20" s="38" t="s">
         <v>54</v>
       </c>
-      <c r="N19" s="44" t="s">
+      <c r="Q20" s="38" t="s">
         <v>55</v>
       </c>
-      <c r="O19" s="44" t="s">
+      <c r="R20" s="38" t="s">
         <v>56</v>
       </c>
-      <c r="P19" s="44" t="s">
+      <c r="S20" s="38" t="s">
         <v>57</v>
       </c>
-      <c r="Q19" s="44" t="s">
-        <v>58</v>
-      </c>
-      <c r="R19" s="44" t="s">
-        <v>59</v>
-      </c>
-      <c r="S19" s="44" t="s">
-        <v>60</v>
-      </c>
-      <c r="T19" s="45">
+      <c r="T20" s="39">
         <f ca="1">COUNTIF(INDIRECT(ADDRESS(ROW(),COLUMN()-15))   : INDIRECT(ADDRESS(ROW(),COLUMN()-1)), "Ф" )</f>
         <v>0</v>
       </c>
-      <c r="U19" s="44" t="s">
+      <c r="U20" s="38" t="s">
+        <v>58</v>
+      </c>
+      <c r="V20" s="38" t="s">
+        <v>59</v>
+      </c>
+      <c r="W20" s="38" t="s">
+        <v>60</v>
+      </c>
+      <c r="X20" s="38" t="s">
         <v>61</v>
       </c>
-      <c r="V19" s="44" t="s">
+      <c r="Y20" s="38" t="s">
         <v>62</v>
       </c>
-      <c r="W19" s="44" t="s">
+      <c r="Z20" s="38" t="s">
         <v>63</v>
       </c>
-      <c r="X19" s="44" t="s">
+      <c r="AA20" s="38" t="s">
         <v>64</v>
       </c>
-      <c r="Y19" s="44" t="s">
+      <c r="AB20" s="38" t="s">
         <v>65</v>
       </c>
-      <c r="Z19" s="44" t="s">
+      <c r="AC20" s="38" t="s">
         <v>66</v>
       </c>
-      <c r="AA19" s="44" t="s">
+      <c r="AD20" s="38" t="s">
         <v>67</v>
       </c>
-      <c r="AB19" s="44" t="s">
+      <c r="AE20" s="38" t="s">
         <v>68</v>
       </c>
-      <c r="AC19" s="44" t="s">
+      <c r="AF20" s="38" t="s">
         <v>69</v>
       </c>
-      <c r="AD19" s="44" t="s">
+      <c r="AG20" s="38" t="s">
         <v>70</v>
       </c>
-      <c r="AE19" s="44" t="s">
+      <c r="AH20" s="38" t="s">
         <v>71</v>
       </c>
-      <c r="AF19" s="44" t="s">
+      <c r="AI20" s="38" t="s">
         <v>72</v>
       </c>
-      <c r="AG19" s="44" t="s">
+      <c r="AJ20" s="38" t="s">
         <v>73</v>
       </c>
-      <c r="AH19" s="44" t="s">
-        <v>74</v>
-      </c>
-      <c r="AI19" s="44" t="s">
-        <v>75</v>
-      </c>
-      <c r="AJ19" s="44" t="s">
-        <v>76</v>
-      </c>
-      <c r="AK19" s="46">
+      <c r="AK20" s="40">
         <f ca="1">COUNTIF(INDIRECT(ADDRESS(ROW(),COLUMN()-32))   : INDIRECT(ADDRESS(ROW(),COLUMN()-1)), "Ф" )</f>
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:46" s="47" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="48" t="s">
-        <v>42</v>
-      </c>
-      <c r="B20" s="49"/>
-      <c r="C20" s="49"/>
-      <c r="D20" s="49"/>
-      <c r="E20" s="43" t="s">
-        <v>84</v>
-      </c>
-      <c r="F20" s="43" t="s">
-        <v>85</v>
-      </c>
-      <c r="G20" s="43" t="s">
-        <v>86</v>
-      </c>
-      <c r="H20" s="43" t="s">
-        <v>87</v>
-      </c>
-      <c r="I20" s="43" t="s">
-        <v>88</v>
-      </c>
-      <c r="J20" s="43" t="s">
-        <v>89</v>
-      </c>
-      <c r="K20" s="43" t="s">
-        <v>90</v>
-      </c>
-      <c r="L20" s="43" t="s">
-        <v>91</v>
-      </c>
-      <c r="M20" s="43" t="s">
-        <v>92</v>
-      </c>
-      <c r="N20" s="43" t="s">
-        <v>93</v>
-      </c>
-      <c r="O20" s="43" t="s">
-        <v>94</v>
-      </c>
-      <c r="P20" s="43" t="s">
-        <v>95</v>
-      </c>
-      <c r="Q20" s="43" t="s">
-        <v>96</v>
-      </c>
-      <c r="R20" s="43" t="s">
-        <v>97</v>
-      </c>
-      <c r="S20" s="43" t="s">
-        <v>98</v>
-      </c>
-      <c r="T20" s="50" t="s">
-        <v>115</v>
-      </c>
-      <c r="U20" s="43" t="s">
-        <v>99</v>
-      </c>
-      <c r="V20" s="43" t="s">
-        <v>100</v>
-      </c>
-      <c r="W20" s="43" t="s">
-        <v>101</v>
-      </c>
-      <c r="X20" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="Y20" s="43" t="s">
-        <v>103</v>
-      </c>
-      <c r="Z20" s="43" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA20" s="43" t="s">
-        <v>105</v>
-      </c>
-      <c r="AB20" s="43" t="s">
-        <v>106</v>
-      </c>
-      <c r="AC20" s="43" t="s">
-        <v>107</v>
-      </c>
-      <c r="AD20" s="43" t="s">
-        <v>108</v>
-      </c>
-      <c r="AE20" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="AF20" s="43" t="s">
-        <v>110</v>
-      </c>
-      <c r="AG20" s="43" t="s">
-        <v>111</v>
-      </c>
-      <c r="AH20" s="43" t="s">
-        <v>112</v>
-      </c>
-      <c r="AI20" s="43" t="s">
-        <v>113</v>
-      </c>
-      <c r="AJ20" s="43" t="s">
+    <row r="21" spans="1:46" s="41" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="45" t="s">
+        <v>78</v>
+      </c>
+      <c r="B21" s="46"/>
+      <c r="C21" s="46"/>
+      <c r="D21" s="46"/>
+      <c r="E21" s="46"/>
+      <c r="F21" s="46"/>
+      <c r="G21" s="46"/>
+      <c r="H21" s="46"/>
+      <c r="I21" s="46"/>
+      <c r="J21" s="46"/>
+      <c r="K21" s="46"/>
+      <c r="L21" s="46"/>
+      <c r="M21" s="46"/>
+      <c r="N21" s="46"/>
+      <c r="O21" s="46"/>
+      <c r="P21" s="46"/>
+      <c r="Q21" s="46"/>
+      <c r="R21" s="46"/>
+      <c r="S21" s="46"/>
+      <c r="T21" s="47" t="e">
+        <f ca="1">SUMPRODUCT(( T19                               : INDIRECT(ADDRESS(ROW()-1,COLUMN())))*ISODD(ROW( T19                               : INDIRECT(ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U21" s="46"/>
+      <c r="V21" s="46"/>
+      <c r="W21" s="46"/>
+      <c r="X21" s="46"/>
+      <c r="Y21" s="46"/>
+      <c r="Z21" s="46"/>
+      <c r="AA21" s="46"/>
+      <c r="AB21" s="46"/>
+      <c r="AC21" s="46"/>
+      <c r="AD21" s="46"/>
+      <c r="AE21" s="46"/>
+      <c r="AF21" s="46"/>
+      <c r="AG21" s="46"/>
+      <c r="AH21" s="46"/>
+      <c r="AI21" s="46"/>
+      <c r="AJ21" s="46"/>
+      <c r="AK21" s="47" t="e">
+        <f ca="1">SUMPRODUCT(( AK19                                 : INDIRECT(ADDRESS(ROW()-1,COLUMN())))*ISODD(ROW( AK19                                 : INDIRECT(ADDRESS(ROW()-1,COLUMN())))))</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="22" spans="1:46" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="1:46" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q23" s="26"/>
+      <c r="R23" s="27"/>
+      <c r="S23" s="27"/>
+      <c r="T23" s="27"/>
+      <c r="U23" s="27"/>
+      <c r="V23" s="27"/>
+      <c r="W23" s="27"/>
+      <c r="X23" s="27"/>
+      <c r="Y23" s="27"/>
+      <c r="Z23" s="27"/>
+      <c r="AA23" s="27"/>
+      <c r="AB23" s="27"/>
+      <c r="AC23" s="27"/>
+      <c r="AD23" s="27"/>
+      <c r="AE23" s="27"/>
+      <c r="AF23" s="27"/>
+      <c r="AG23" s="27"/>
+      <c r="AH23" s="27"/>
+      <c r="AI23" s="27"/>
+      <c r="AJ23" s="27"/>
+      <c r="AK23" s="28"/>
+    </row>
+    <row r="24" spans="1:46" s="20" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="72" t="s">
         <v>114</v>
       </c>
-      <c r="AK20" s="50" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="21" spans="1:46" s="54" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="51" t="s">
-        <v>83</v>
-      </c>
-      <c r="B21" s="52"/>
-      <c r="C21" s="52"/>
-      <c r="D21" s="52"/>
-      <c r="E21" s="52"/>
-      <c r="F21" s="52"/>
-      <c r="G21" s="52"/>
-      <c r="H21" s="52"/>
-      <c r="I21" s="52"/>
-      <c r="J21" s="52"/>
-      <c r="K21" s="52"/>
-      <c r="L21" s="52"/>
-      <c r="M21" s="52"/>
-      <c r="N21" s="52"/>
-      <c r="O21" s="52"/>
-      <c r="P21" s="52"/>
-      <c r="Q21" s="52"/>
-      <c r="R21" s="52"/>
-      <c r="S21" s="52"/>
-      <c r="T21" s="53" t="e">
-        <f ca="1">SUMPRODUCT(( T20                   : INDIRECT(ADDRESS(ROW()-1,COLUMN())))*ISEVEN(ROW( T20                   : INDIRECT(ADDRESS(ROW()-1,COLUMN())))))</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="U21" s="52"/>
-      <c r="V21" s="52"/>
-      <c r="W21" s="52"/>
-      <c r="X21" s="52"/>
-      <c r="Y21" s="52"/>
-      <c r="Z21" s="52"/>
-      <c r="AA21" s="52"/>
-      <c r="AB21" s="52"/>
-      <c r="AC21" s="52"/>
-      <c r="AD21" s="52"/>
-      <c r="AE21" s="52"/>
-      <c r="AF21" s="52"/>
-      <c r="AG21" s="52"/>
-      <c r="AH21" s="52"/>
-      <c r="AI21" s="52"/>
-      <c r="AJ21" s="52"/>
-      <c r="AK21" s="53" t="e">
-        <f ca="1">SUMPRODUCT(( AK20                      : INDIRECT(ADDRESS(ROW()-1,COLUMN())))*ISEVEN(ROW( AK20                      : INDIRECT(ADDRESS(ROW()-1,COLUMN())))))</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="22" spans="1:46" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="23" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="Q23" s="31"/>
-      <c r="R23" s="32"/>
-      <c r="S23" s="32"/>
-      <c r="T23" s="32"/>
-      <c r="U23" s="32"/>
-      <c r="V23" s="32"/>
-      <c r="W23" s="32"/>
-      <c r="X23" s="32"/>
-      <c r="Y23" s="32"/>
-      <c r="Z23" s="32"/>
-      <c r="AA23" s="32"/>
-      <c r="AB23" s="32"/>
-      <c r="AC23" s="32"/>
-      <c r="AD23" s="32"/>
-      <c r="AE23" s="32"/>
-      <c r="AF23" s="32"/>
-      <c r="AG23" s="32"/>
-      <c r="AH23" s="32"/>
-      <c r="AI23" s="32"/>
-      <c r="AJ23" s="32"/>
-      <c r="AK23" s="33"/>
-    </row>
-    <row r="24" spans="1:46" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="B24" s="26"/>
-      <c r="C24" s="26"/>
-      <c r="E24" s="26" t="s">
+      <c r="B24" s="72"/>
+      <c r="C24" s="72"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="21"/>
+      <c r="F24" s="21"/>
+      <c r="G24" s="21"/>
+      <c r="H24" s="72" t="s">
+        <v>30</v>
+      </c>
+      <c r="I24" s="72"/>
+      <c r="J24" s="72"/>
+      <c r="K24" s="72"/>
+      <c r="L24" s="72"/>
+      <c r="M24" s="72"/>
+      <c r="Q24" s="29"/>
+      <c r="T24" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="AK24" s="31"/>
+    </row>
+    <row r="25" spans="1:46" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D25" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="H25" s="72" t="s">
+        <v>118</v>
+      </c>
+      <c r="I25" s="72"/>
+      <c r="J25" s="72"/>
+      <c r="K25" s="73"/>
+      <c r="L25" s="72"/>
+      <c r="M25" s="72"/>
+      <c r="Q25" s="29"/>
+      <c r="AK25" s="31"/>
+    </row>
+    <row r="26" spans="1:46" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="72" t="s">
+        <v>32</v>
+      </c>
+      <c r="B26" s="72"/>
+      <c r="C26" s="72"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="21"/>
+      <c r="F26" s="21"/>
+      <c r="G26" s="21"/>
+      <c r="H26" s="72" t="s">
+        <v>31</v>
+      </c>
+      <c r="I26" s="72"/>
+      <c r="J26" s="72"/>
+      <c r="K26" s="72"/>
+      <c r="L26" s="72"/>
+      <c r="M26" s="72"/>
+      <c r="Q26" s="29"/>
+      <c r="R26" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="U26" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y26" s="21"/>
+      <c r="Z26" s="21"/>
+      <c r="AA26" s="21"/>
+      <c r="AB26" s="21"/>
+      <c r="AC26" s="21"/>
+      <c r="AD26" s="21"/>
+      <c r="AE26" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="AK26" s="31"/>
+    </row>
+    <row r="27" spans="1:46" s="20" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D27" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="H27" s="72" t="s">
+        <v>118</v>
+      </c>
+      <c r="I27" s="72"/>
+      <c r="J27" s="72"/>
+      <c r="K27" s="72"/>
+      <c r="L27" s="72"/>
+      <c r="M27" s="72"/>
+      <c r="Q27" s="29"/>
+      <c r="S27" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="AK27" s="31"/>
+    </row>
+    <row r="28" spans="1:46" s="20" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q28" s="29"/>
+      <c r="AK28" s="31"/>
+    </row>
+    <row r="29" spans="1:46" s="20" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q29" s="29"/>
+      <c r="R29" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="AK29" s="31"/>
+    </row>
+    <row r="30" spans="1:46" s="20" customFormat="1" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="F24" s="26"/>
-      <c r="G24" s="26"/>
-      <c r="H24" s="26"/>
-      <c r="I24" s="26"/>
-      <c r="J24" s="26"/>
-      <c r="K24" s="26"/>
-      <c r="L24" s="26"/>
-      <c r="M24" s="26"/>
-      <c r="N24" s="26"/>
-      <c r="O24" s="26"/>
-      <c r="Q24" s="34"/>
-      <c r="T24" s="35" t="s">
-        <v>20</v>
-      </c>
-      <c r="AK24" s="36"/>
-    </row>
-    <row r="25" spans="1:46" s="25" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E25" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q25" s="34"/>
-      <c r="AK25" s="36"/>
-    </row>
-    <row r="26" spans="1:46" s="25" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="B26" s="26"/>
-      <c r="C26" s="26"/>
-      <c r="E26" s="26" t="s">
-        <v>34</v>
-      </c>
-      <c r="F26" s="26"/>
-      <c r="G26" s="26"/>
-      <c r="H26" s="26"/>
-      <c r="I26" s="26"/>
-      <c r="J26" s="26"/>
-      <c r="K26" s="26"/>
-      <c r="L26" s="26"/>
-      <c r="M26" s="26"/>
-      <c r="N26" s="26"/>
-      <c r="O26" s="26"/>
-      <c r="Q26" s="34"/>
-      <c r="R26" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="U26" s="41" t="s">
-        <v>80</v>
-      </c>
-      <c r="Y26" s="25" t="s">
-        <v>79</v>
-      </c>
-      <c r="AC26" s="41" t="s">
-        <v>81</v>
-      </c>
-      <c r="AK26" s="36"/>
-    </row>
-    <row r="27" spans="1:46" s="25" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E27" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q27" s="34"/>
-      <c r="S27" s="25" t="s">
-        <v>6</v>
-      </c>
-      <c r="AK27" s="36"/>
-    </row>
-    <row r="28" spans="1:46" s="25" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="Q28" s="34"/>
-      <c r="AK28" s="36"/>
-    </row>
-    <row r="29" spans="1:46" s="25" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="Q29" s="34"/>
-      <c r="R29" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="AK29" s="36"/>
-    </row>
-    <row r="30" spans="1:46" s="25" customFormat="1" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="25" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q30" s="37"/>
-      <c r="R30" s="38"/>
-      <c r="S30" s="38"/>
-      <c r="T30" s="38"/>
-      <c r="U30" s="38"/>
-      <c r="V30" s="38"/>
-      <c r="W30" s="38"/>
-      <c r="X30" s="38"/>
-      <c r="Y30" s="38"/>
-      <c r="Z30" s="38"/>
-      <c r="AA30" s="38"/>
-      <c r="AB30" s="38"/>
-      <c r="AC30" s="38"/>
-      <c r="AD30" s="38"/>
-      <c r="AE30" s="38"/>
-      <c r="AF30" s="38"/>
-      <c r="AG30" s="38"/>
-      <c r="AH30" s="38"/>
-      <c r="AI30" s="38"/>
-      <c r="AJ30" s="38"/>
-      <c r="AK30" s="39"/>
-    </row>
-    <row r="31" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+      <c r="H30"/>
+      <c r="Q30" s="32"/>
+      <c r="R30" s="33"/>
+      <c r="S30" s="33"/>
+      <c r="T30" s="33"/>
+      <c r="U30" s="33"/>
+      <c r="V30" s="33"/>
+      <c r="W30" s="33"/>
+      <c r="X30" s="33"/>
+      <c r="Y30" s="33"/>
+      <c r="Z30" s="33"/>
+      <c r="AA30" s="33"/>
+      <c r="AB30" s="33"/>
+      <c r="AC30" s="33"/>
+      <c r="AD30" s="33"/>
+      <c r="AE30" s="33"/>
+      <c r="AF30" s="33"/>
+      <c r="AG30" s="33"/>
+      <c r="AH30" s="33"/>
+      <c r="AI30" s="33"/>
+      <c r="AJ30" s="33"/>
+      <c r="AK30" s="34"/>
+    </row>
+    <row r="31" spans="1:46" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="377" spans="1:46" x14ac:dyDescent="0.2">
+      <c r="H377" s="1"/>
+    </row>
     <row r="378" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A378" s="1"/>
       <c r="B378" s="1"/>
@@ -13529,7 +13564,6 @@
       <c r="E605" s="1"/>
       <c r="F605" s="1"/>
       <c r="G605" s="1"/>
-      <c r="H605" s="1"/>
       <c r="I605" s="1"/>
       <c r="J605" s="1"/>
       <c r="K605" s="1"/>
@@ -13570,7 +13604,14 @@
       <c r="AT605" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="15">
+    <mergeCell ref="AI9:AK9"/>
+    <mergeCell ref="AG1:AK1"/>
+    <mergeCell ref="AI4:AK4"/>
+    <mergeCell ref="H2:U2"/>
+    <mergeCell ref="D6:AB6"/>
+    <mergeCell ref="AI5:AK5"/>
+    <mergeCell ref="E3:Y3"/>
     <mergeCell ref="B12:B17"/>
     <mergeCell ref="C12:C17"/>
     <mergeCell ref="D7:AB7"/>
@@ -13579,12 +13620,6 @@
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="D8:AB8"/>
     <mergeCell ref="A8:B8"/>
-    <mergeCell ref="AG1:AK1"/>
-    <mergeCell ref="AI4:AK4"/>
-    <mergeCell ref="H2:U2"/>
-    <mergeCell ref="D6:AB6"/>
-    <mergeCell ref="AI5:AK5"/>
-    <mergeCell ref="E3:Y3"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.19685039370078741" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
